--- a/OUTPUT/direct_A0QVY5_Mycobacterium_smegmatis_str__MC2_155.xlsx
+++ b/OUTPUT/direct_A0QVY5_Mycobacterium_smegmatis_str__MC2_155.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.9378</v>
+        <v>0.937624950019992</v>
       </c>
     </row>
   </sheetData>
